--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:15:37</t>
+          <t>2026-05-24 05:27:41</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:27:41</t>
+          <t>2026-05-25 14:24:37</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:24:37</t>
+          <t>2026-05-26 14:15:24</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3483.3837</v>
+        <v>3484.8686</v>
       </c>
       <c r="O2" t="n">
         <v>95</v>
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -565,25 +565,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H3" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -601,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3473.152</v>
+        <v>3475.262</v>
       </c>
       <c r="O3" t="n">
         <v>94.90000000000001</v>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -622,25 +622,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>29</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
         <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3471.8366</v>
+        <v>3474.3749</v>
       </c>
       <c r="O4" t="n">
-        <v>94.88</v>
+        <v>94.89</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -679,25 +679,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -715,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3470.6002</v>
+        <v>3473.5071</v>
       </c>
       <c r="O5" t="n">
-        <v>94.87</v>
+        <v>94.89</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -736,25 +736,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -772,10 +772,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3469.3069</v>
+        <v>3472.5412</v>
       </c>
       <c r="O6" t="n">
-        <v>94.86</v>
+        <v>94.88</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -793,25 +793,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -826,13 +826,13 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>3467.2797</v>
+        <v>3470.6996</v>
       </c>
       <c r="O7" t="n">
-        <v>94.84</v>
+        <v>94.86</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -850,25 +850,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
         <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -883,10 +883,10 @@
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>3467.2779</v>
+        <v>3469.0736</v>
       </c>
       <c r="O8" t="n">
         <v>94.84</v>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -907,25 +907,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31</v>
+      </c>
+      <c r="F9" t="n">
+        <v>41</v>
+      </c>
+      <c r="G9" t="n">
         <v>15</v>
       </c>
-      <c r="D9" t="n">
-        <v>24</v>
-      </c>
-      <c r="E9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F9" t="n">
-        <v>36</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
       <c r="H9" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3466.7604</v>
+        <v>3469.059</v>
       </c>
       <c r="O9" t="n">
-        <v>94.83</v>
+        <v>94.84</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -964,22 +964,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>37</v>
+      </c>
+      <c r="G10" t="n">
         <v>12</v>
-      </c>
-      <c r="C10" t="n">
-        <v>15</v>
-      </c>
-      <c r="D10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E10" t="n">
-        <v>29</v>
-      </c>
-      <c r="F10" t="n">
-        <v>45</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11</v>
       </c>
       <c r="H10" t="n">
         <v>121</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3465.2183</v>
+        <v>3467.9218</v>
       </c>
       <c r="O10" t="n">
-        <v>94.81999999999999</v>
+        <v>94.83</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>
@@ -1021,25 +1021,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
         <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -1054,13 +1054,13 @@
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3465.0221</v>
+        <v>3467.5828</v>
       </c>
       <c r="O11" t="n">
-        <v>94.81999999999999</v>
+        <v>94.83</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:15:24</t>
+          <t>2026-05-27 14:48:56</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:48:56</t>
+          <t>2026-05-28 08:47:08</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:47:08</t>
+          <t>2026-05-28 17:13:00</t>
         </is>
       </c>
     </row>

--- a/data/exports/predictions/powerball_predictions.xlsx
+++ b/data/exports/predictions/powerball_predictions.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -955,7 +955,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:13:00</t>
+          <t>2026-05-28 19:42:41</t>
         </is>
       </c>
     </row>
